--- a/artfynd/A 32104-2026 artfynd.xlsx
+++ b/artfynd/A 32104-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136794273</v>
       </c>
       <c r="B2" t="n">
-        <v>92074</v>
+        <v>92076</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136794300</v>
       </c>
       <c r="B3" t="n">
-        <v>92074</v>
+        <v>92076</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136794318</v>
       </c>
       <c r="B4" t="n">
-        <v>92074</v>
+        <v>92076</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136794327</v>
       </c>
       <c r="B5" t="n">
-        <v>92074</v>
+        <v>92076</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>136794384</v>
       </c>
       <c r="B6" t="n">
-        <v>92074</v>
+        <v>92076</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>136794418</v>
       </c>
       <c r="B7" t="n">
-        <v>92074</v>
+        <v>92076</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2569,7 +2569,7 @@
         <v>136793640</v>
       </c>
       <c r="B19" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2689,7 +2689,7 @@
         <v>136793838</v>
       </c>
       <c r="B20" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2809,7 +2809,7 @@
         <v>136794393</v>
       </c>
       <c r="B21" t="n">
-        <v>92503</v>
+        <v>92505</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 32104-2026 artfynd.xlsx
+++ b/artfynd/A 32104-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136794273</v>
       </c>
       <c r="B2" t="n">
-        <v>92076</v>
+        <v>92078</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136794300</v>
       </c>
       <c r="B3" t="n">
-        <v>92076</v>
+        <v>92078</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136794318</v>
       </c>
       <c r="B4" t="n">
-        <v>92076</v>
+        <v>92078</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136794327</v>
       </c>
       <c r="B5" t="n">
-        <v>92076</v>
+        <v>92078</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>136794384</v>
       </c>
       <c r="B6" t="n">
-        <v>92076</v>
+        <v>92078</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>136794418</v>
       </c>
       <c r="B7" t="n">
-        <v>92076</v>
+        <v>92078</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>136793710</v>
       </c>
       <c r="B8" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         <v>136793725</v>
       </c>
       <c r="B9" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1563,7 +1563,7 @@
         <v>136793752</v>
       </c>
       <c r="B10" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
         <v>136793769</v>
       </c>
       <c r="B11" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>136793857</v>
       </c>
       <c r="B12" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1898,7 +1898,7 @@
         <v>136793863</v>
       </c>
       <c r="B13" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2008,7 +2008,7 @@
         <v>136794132</v>
       </c>
       <c r="B14" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2118,7 +2118,7 @@
         <v>136794369</v>
       </c>
       <c r="B15" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2569,7 +2569,7 @@
         <v>136793640</v>
       </c>
       <c r="B19" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2689,7 +2689,7 @@
         <v>136793838</v>
       </c>
       <c r="B20" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2809,7 +2809,7 @@
         <v>136794393</v>
       </c>
       <c r="B21" t="n">
-        <v>92505</v>
+        <v>92507</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 32104-2026 artfynd.xlsx
+++ b/artfynd/A 32104-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136794273</v>
       </c>
       <c r="B2" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136794300</v>
       </c>
       <c r="B3" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136794318</v>
       </c>
       <c r="B4" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136794327</v>
       </c>
       <c r="B5" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>136794384</v>
       </c>
       <c r="B6" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>136794418</v>
       </c>
       <c r="B7" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>136793710</v>
       </c>
       <c r="B8" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         <v>136793725</v>
       </c>
       <c r="B9" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1563,7 +1563,7 @@
         <v>136793752</v>
       </c>
       <c r="B10" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
         <v>136793769</v>
       </c>
       <c r="B11" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>136793857</v>
       </c>
       <c r="B12" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1898,7 +1898,7 @@
         <v>136793863</v>
       </c>
       <c r="B13" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2008,7 +2008,7 @@
         <v>136794132</v>
       </c>
       <c r="B14" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2118,7 +2118,7 @@
         <v>136794369</v>
       </c>
       <c r="B15" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2569,7 +2569,7 @@
         <v>136793640</v>
       </c>
       <c r="B19" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2689,7 +2689,7 @@
         <v>136793838</v>
       </c>
       <c r="B20" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2809,7 +2809,7 @@
         <v>136794393</v>
       </c>
       <c r="B21" t="n">
-        <v>92507</v>
+        <v>92509</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 32104-2026 artfynd.xlsx
+++ b/artfynd/A 32104-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136794273</v>
       </c>
       <c r="B2" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136794300</v>
       </c>
       <c r="B3" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136794318</v>
       </c>
       <c r="B4" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136794327</v>
       </c>
       <c r="B5" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>136794384</v>
       </c>
       <c r="B6" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>136794418</v>
       </c>
       <c r="B7" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>136793710</v>
       </c>
       <c r="B8" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         <v>136793725</v>
       </c>
       <c r="B9" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1563,7 +1563,7 @@
         <v>136793752</v>
       </c>
       <c r="B10" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
         <v>136793769</v>
       </c>
       <c r="B11" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>136793857</v>
       </c>
       <c r="B12" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1898,7 +1898,7 @@
         <v>136793863</v>
       </c>
       <c r="B13" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2008,7 +2008,7 @@
         <v>136794132</v>
       </c>
       <c r="B14" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2118,7 +2118,7 @@
         <v>136794369</v>
       </c>
       <c r="B15" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2569,7 +2569,7 @@
         <v>136793640</v>
       </c>
       <c r="B19" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2689,7 +2689,7 @@
         <v>136793838</v>
       </c>
       <c r="B20" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2809,7 +2809,7 @@
         <v>136794393</v>
       </c>
       <c r="B21" t="n">
-        <v>92509</v>
+        <v>92510</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 32104-2026 artfynd.xlsx
+++ b/artfynd/A 32104-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136794273</v>
       </c>
       <c r="B2" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136794300</v>
       </c>
       <c r="B3" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136794318</v>
       </c>
       <c r="B4" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136794327</v>
       </c>
       <c r="B5" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>136794384</v>
       </c>
       <c r="B6" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>136794418</v>
       </c>
       <c r="B7" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2569,7 +2569,7 @@
         <v>136793640</v>
       </c>
       <c r="B19" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2689,7 +2689,7 @@
         <v>136793838</v>
       </c>
       <c r="B20" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2809,7 +2809,7 @@
         <v>136794393</v>
       </c>
       <c r="B21" t="n">
-        <v>92510</v>
+        <v>92516</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 32104-2026 artfynd.xlsx
+++ b/artfynd/A 32104-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136794273</v>
       </c>
       <c r="B2" t="n">
-        <v>92087</v>
+        <v>92091</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136794300</v>
       </c>
       <c r="B3" t="n">
-        <v>92087</v>
+        <v>92091</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136794318</v>
       </c>
       <c r="B4" t="n">
-        <v>92087</v>
+        <v>92091</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136794327</v>
       </c>
       <c r="B5" t="n">
-        <v>92087</v>
+        <v>92091</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>136794384</v>
       </c>
       <c r="B6" t="n">
-        <v>92087</v>
+        <v>92091</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>136794418</v>
       </c>
       <c r="B7" t="n">
-        <v>92087</v>
+        <v>92091</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>136793710</v>
       </c>
       <c r="B8" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         <v>136793725</v>
       </c>
       <c r="B9" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1563,7 +1563,7 @@
         <v>136793752</v>
       </c>
       <c r="B10" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
         <v>136793769</v>
       </c>
       <c r="B11" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>136793857</v>
       </c>
       <c r="B12" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1898,7 +1898,7 @@
         <v>136793863</v>
       </c>
       <c r="B13" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2008,7 +2008,7 @@
         <v>136794132</v>
       </c>
       <c r="B14" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2118,7 +2118,7 @@
         <v>136794369</v>
       </c>
       <c r="B15" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2569,7 +2569,7 @@
         <v>136793640</v>
       </c>
       <c r="B19" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2689,7 +2689,7 @@
         <v>136793838</v>
       </c>
       <c r="B20" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2809,7 +2809,7 @@
         <v>136794393</v>
       </c>
       <c r="B21" t="n">
-        <v>92516</v>
+        <v>92520</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 32104-2026 artfynd.xlsx
+++ b/artfynd/A 32104-2026 artfynd.xlsx
@@ -2569,7 +2569,7 @@
         <v>136793640</v>
       </c>
       <c r="B19" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2689,7 +2689,7 @@
         <v>136793838</v>
       </c>
       <c r="B20" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 32104-2026 artfynd.xlsx
+++ b/artfynd/A 32104-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136794273</v>
       </c>
       <c r="B2" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136794300</v>
       </c>
       <c r="B3" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136794318</v>
       </c>
       <c r="B4" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136794327</v>
       </c>
       <c r="B5" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>136794384</v>
       </c>
       <c r="B6" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>136794418</v>
       </c>
       <c r="B7" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>136793710</v>
       </c>
       <c r="B8" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         <v>136793725</v>
       </c>
       <c r="B9" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1563,7 +1563,7 @@
         <v>136793752</v>
       </c>
       <c r="B10" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
         <v>136793769</v>
       </c>
       <c r="B11" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>136793857</v>
       </c>
       <c r="B12" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1898,7 +1898,7 @@
         <v>136793863</v>
       </c>
       <c r="B13" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2008,7 +2008,7 @@
         <v>136794132</v>
       </c>
       <c r="B14" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2118,7 +2118,7 @@
         <v>136794369</v>
       </c>
       <c r="B15" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2569,7 +2569,7 @@
         <v>136793640</v>
       </c>
       <c r="B19" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2689,7 +2689,7 @@
         <v>136793838</v>
       </c>
       <c r="B20" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2809,7 +2809,7 @@
         <v>136794393</v>
       </c>
       <c r="B21" t="n">
-        <v>92520</v>
+        <v>92522</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 32104-2026 artfynd.xlsx
+++ b/artfynd/A 32104-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136794273</v>
       </c>
       <c r="B2" t="n">
-        <v>92093</v>
+        <v>92106</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136794300</v>
       </c>
       <c r="B3" t="n">
-        <v>92093</v>
+        <v>92106</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136794318</v>
       </c>
       <c r="B4" t="n">
-        <v>92093</v>
+        <v>92106</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136794327</v>
       </c>
       <c r="B5" t="n">
-        <v>92093</v>
+        <v>92106</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>136794384</v>
       </c>
       <c r="B6" t="n">
-        <v>92093</v>
+        <v>92106</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>136794418</v>
       </c>
       <c r="B7" t="n">
-        <v>92093</v>
+        <v>92106</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>136793710</v>
       </c>
       <c r="B8" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         <v>136793725</v>
       </c>
       <c r="B9" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1563,7 +1563,7 @@
         <v>136793752</v>
       </c>
       <c r="B10" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
         <v>136793769</v>
       </c>
       <c r="B11" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>136793857</v>
       </c>
       <c r="B12" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1898,7 +1898,7 @@
         <v>136793863</v>
       </c>
       <c r="B13" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2008,7 +2008,7 @@
         <v>136794132</v>
       </c>
       <c r="B14" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2118,7 +2118,7 @@
         <v>136794369</v>
       </c>
       <c r="B15" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         <v>136794336</v>
       </c>
       <c r="B16" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2343,7 +2343,7 @@
         <v>136794357</v>
       </c>
       <c r="B17" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2458,7 +2458,7 @@
         <v>136793715</v>
       </c>
       <c r="B18" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2569,7 +2569,7 @@
         <v>136793640</v>
       </c>
       <c r="B19" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2689,7 +2689,7 @@
         <v>136793838</v>
       </c>
       <c r="B20" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2809,7 +2809,7 @@
         <v>136794393</v>
       </c>
       <c r="B21" t="n">
-        <v>92522</v>
+        <v>92535</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 32104-2026 artfynd.xlsx
+++ b/artfynd/A 32104-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136794273</v>
       </c>
       <c r="B2" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136794300</v>
       </c>
       <c r="B3" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136794318</v>
       </c>
       <c r="B4" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136794327</v>
       </c>
       <c r="B5" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>136794384</v>
       </c>
       <c r="B6" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>136794418</v>
       </c>
       <c r="B7" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>136793710</v>
       </c>
       <c r="B8" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         <v>136793725</v>
       </c>
       <c r="B9" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1563,7 +1563,7 @@
         <v>136793752</v>
       </c>
       <c r="B10" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
         <v>136793769</v>
       </c>
       <c r="B11" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>136793857</v>
       </c>
       <c r="B12" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1898,7 +1898,7 @@
         <v>136793863</v>
       </c>
       <c r="B13" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2008,7 +2008,7 @@
         <v>136794132</v>
       </c>
       <c r="B14" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2118,7 +2118,7 @@
         <v>136794369</v>
       </c>
       <c r="B15" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         <v>136794336</v>
       </c>
       <c r="B16" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2343,7 +2343,7 @@
         <v>136794357</v>
       </c>
       <c r="B17" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2458,7 +2458,7 @@
         <v>136793715</v>
       </c>
       <c r="B18" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2569,7 +2569,7 @@
         <v>136793640</v>
       </c>
       <c r="B19" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2689,7 +2689,7 @@
         <v>136793838</v>
       </c>
       <c r="B20" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2809,7 +2809,7 @@
         <v>136794393</v>
       </c>
       <c r="B21" t="n">
-        <v>92535</v>
+        <v>92537</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 32104-2026 artfynd.xlsx
+++ b/artfynd/A 32104-2026 artfynd.xlsx
@@ -2256,11 +2256,7 @@
       <c r="I16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2371,11 +2367,7 @@
       <c r="I17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2600,11 +2592,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
@@ -2720,11 +2708,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">

--- a/artfynd/A 32104-2026 artfynd.xlsx
+++ b/artfynd/A 32104-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136794273</v>
       </c>
       <c r="B2" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136794300</v>
       </c>
       <c r="B3" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136794318</v>
       </c>
       <c r="B4" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136794327</v>
       </c>
       <c r="B5" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>136794384</v>
       </c>
       <c r="B6" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>136794418</v>
       </c>
       <c r="B7" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2561,7 +2561,7 @@
         <v>136793640</v>
       </c>
       <c r="B19" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2677,7 +2677,7 @@
         <v>136793838</v>
       </c>
       <c r="B20" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2793,7 +2793,7 @@
         <v>136794393</v>
       </c>
       <c r="B21" t="n">
-        <v>92537</v>
+        <v>92540</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 32104-2026 artfynd.xlsx
+++ b/artfynd/A 32104-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136794273</v>
       </c>
       <c r="B2" t="n">
-        <v>92111</v>
+        <v>92121</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136794300</v>
       </c>
       <c r="B3" t="n">
-        <v>92111</v>
+        <v>92121</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136794318</v>
       </c>
       <c r="B4" t="n">
-        <v>92111</v>
+        <v>92121</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136794327</v>
       </c>
       <c r="B5" t="n">
-        <v>92111</v>
+        <v>92121</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>136794384</v>
       </c>
       <c r="B6" t="n">
-        <v>92111</v>
+        <v>92121</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>136794418</v>
       </c>
       <c r="B7" t="n">
-        <v>92111</v>
+        <v>92121</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>136793710</v>
       </c>
       <c r="B8" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         <v>136793725</v>
       </c>
       <c r="B9" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1563,7 +1563,7 @@
         <v>136793752</v>
       </c>
       <c r="B10" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
         <v>136793769</v>
       </c>
       <c r="B11" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>136793857</v>
       </c>
       <c r="B12" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1898,7 +1898,7 @@
         <v>136793863</v>
       </c>
       <c r="B13" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2008,7 +2008,7 @@
         <v>136794132</v>
       </c>
       <c r="B14" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2118,7 +2118,7 @@
         <v>136794369</v>
       </c>
       <c r="B15" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         <v>136794336</v>
       </c>
       <c r="B16" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2339,7 +2339,7 @@
         <v>136794357</v>
       </c>
       <c r="B17" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2450,7 +2450,7 @@
         <v>136793715</v>
       </c>
       <c r="B18" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2561,7 +2561,7 @@
         <v>136793640</v>
       </c>
       <c r="B19" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2677,7 +2677,7 @@
         <v>136793838</v>
       </c>
       <c r="B20" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2793,7 +2793,7 @@
         <v>136794393</v>
       </c>
       <c r="B21" t="n">
-        <v>92540</v>
+        <v>92550</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 32104-2026 artfynd.xlsx
+++ b/artfynd/A 32104-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136794273</v>
       </c>
       <c r="B2" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136794300</v>
       </c>
       <c r="B3" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136794318</v>
       </c>
       <c r="B4" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136794327</v>
       </c>
       <c r="B5" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>136794384</v>
       </c>
       <c r="B6" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>136794418</v>
       </c>
       <c r="B7" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2561,7 +2561,7 @@
         <v>136793640</v>
       </c>
       <c r="B19" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2677,7 +2677,7 @@
         <v>136793838</v>
       </c>
       <c r="B20" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2793,7 +2793,7 @@
         <v>136794393</v>
       </c>
       <c r="B21" t="n">
-        <v>92550</v>
+        <v>92551</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 32104-2026 artfynd.xlsx
+++ b/artfynd/A 32104-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136794273</v>
       </c>
       <c r="B2" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136794300</v>
       </c>
       <c r="B3" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136794318</v>
       </c>
       <c r="B4" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136794327</v>
       </c>
       <c r="B5" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>136794384</v>
       </c>
       <c r="B6" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>136794418</v>
       </c>
       <c r="B7" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>136793710</v>
       </c>
       <c r="B8" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         <v>136793725</v>
       </c>
       <c r="B9" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1563,7 +1563,7 @@
         <v>136793752</v>
       </c>
       <c r="B10" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
         <v>136793769</v>
       </c>
       <c r="B11" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>136793857</v>
       </c>
       <c r="B12" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1898,7 +1898,7 @@
         <v>136793863</v>
       </c>
       <c r="B13" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2008,7 +2008,7 @@
         <v>136794132</v>
       </c>
       <c r="B14" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2118,7 +2118,7 @@
         <v>136794369</v>
       </c>
       <c r="B15" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         <v>136794336</v>
       </c>
       <c r="B16" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2339,7 +2339,7 @@
         <v>136794357</v>
       </c>
       <c r="B17" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2450,7 +2450,7 @@
         <v>136793715</v>
       </c>
       <c r="B18" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2561,7 +2561,7 @@
         <v>136793640</v>
       </c>
       <c r="B19" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2677,7 +2677,7 @@
         <v>136793838</v>
       </c>
       <c r="B20" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2793,7 +2793,7 @@
         <v>136794393</v>
       </c>
       <c r="B21" t="n">
-        <v>92551</v>
+        <v>92554</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 32104-2026 artfynd.xlsx
+++ b/artfynd/A 32104-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136794273</v>
       </c>
       <c r="B2" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136794300</v>
       </c>
       <c r="B3" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136794318</v>
       </c>
       <c r="B4" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136794327</v>
       </c>
       <c r="B5" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>136794384</v>
       </c>
       <c r="B6" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>136794418</v>
       </c>
       <c r="B7" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2561,7 +2561,7 @@
         <v>136793640</v>
       </c>
       <c r="B19" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2677,7 +2677,7 @@
         <v>136793838</v>
       </c>
       <c r="B20" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2793,7 +2793,7 @@
         <v>136794393</v>
       </c>
       <c r="B21" t="n">
-        <v>92554</v>
+        <v>92556</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 32104-2026 artfynd.xlsx
+++ b/artfynd/A 32104-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136794273</v>
       </c>
       <c r="B2" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136794300</v>
       </c>
       <c r="B3" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136794318</v>
       </c>
       <c r="B4" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136794327</v>
       </c>
       <c r="B5" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>136794384</v>
       </c>
       <c r="B6" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>136794418</v>
       </c>
       <c r="B7" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>136793710</v>
       </c>
       <c r="B8" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         <v>136793725</v>
       </c>
       <c r="B9" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1563,7 +1563,7 @@
         <v>136793752</v>
       </c>
       <c r="B10" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
         <v>136793769</v>
       </c>
       <c r="B11" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>136793857</v>
       </c>
       <c r="B12" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1898,7 +1898,7 @@
         <v>136793863</v>
       </c>
       <c r="B13" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2008,7 +2008,7 @@
         <v>136794132</v>
       </c>
       <c r="B14" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2118,7 +2118,7 @@
         <v>136794369</v>
       </c>
       <c r="B15" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         <v>136794336</v>
       </c>
       <c r="B16" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2339,7 +2339,7 @@
         <v>136794357</v>
       </c>
       <c r="B17" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2450,7 +2450,7 @@
         <v>136793715</v>
       </c>
       <c r="B18" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2561,7 +2561,7 @@
         <v>136793640</v>
       </c>
       <c r="B19" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2677,7 +2677,7 @@
         <v>136793838</v>
       </c>
       <c r="B20" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2793,7 +2793,7 @@
         <v>136794393</v>
       </c>
       <c r="B21" t="n">
-        <v>92556</v>
+        <v>92561</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
